--- a/public/templates/template_contracts.xlsx
+++ b/public/templates/template_contracts.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -412,6 +412,7 @@
     <col min="11" max="11" width="18.83203125" customWidth="1"/>
     <col min="12" max="12" width="18.83203125" customWidth="1"/>
     <col min="13" max="13" width="18.83203125" customWidth="1"/>
+    <col min="14" max="14" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +455,9 @@
       <c r="M1" t="str">
         <v>رقم الصك</v>
       </c>
+      <c r="N1" t="str">
+        <v>الاسم التجاري</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -469,7 +473,7 @@
         <v>أحمد الشهري</v>
       </c>
       <c r="E2" t="str">
-        <v>2087654321</v>
+        <v>1087654321</v>
       </c>
       <c r="F2" t="str">
         <v>2026-01-01</v>
@@ -494,11 +498,14 @@
       </c>
       <c r="M2" t="str">
         <v>3100012345</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N2"/>
   </ignoredErrors>
 </worksheet>
 </file>